--- a/Collections/EURO/Austria/#EURO#Austria#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Austria/#EURO#Austria#Regular#[2002-present]#circulation_quality.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Austria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B345B61E-D1E8-4B86-833A-553E6FBBA208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8892D670-F24B-4414-98A2-B6F1BB278B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="33150" windowHeight="17700" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -372,7 +375,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="675" uniqueCount="96">
   <si>
     <t>-</t>
   </si>
@@ -639,6 +642,27 @@
   </si>
   <si>
     <t>Subtype_2#Map_of_Europe</t>
+  </si>
+  <si>
+    <t>28.700.000</t>
+  </si>
+  <si>
+    <t>32.700.000</t>
+  </si>
+  <si>
+    <t>14.300.000</t>
+  </si>
+  <si>
+    <t>26.600.000</t>
+  </si>
+  <si>
+    <t>23.200.000</t>
+  </si>
+  <si>
+    <t>5.800.000</t>
+  </si>
+  <si>
+    <t>25.700.000</t>
   </si>
 </sst>
 </file>
@@ -1458,7 +1482,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -1987,7 +2011,49 @@
         <v>0</v>
       </c>
       <c r="G24" s="4" t="str">
-        <f t="shared" ref="G24" si="2">IF(OR(AND(F24&gt;1,F24&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G24:G25" si="2">IF(OR(AND(F24&gt;1,F24&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="14"/>
+      <c r="E25" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" ref="G26" si="3">IF(OR(AND(F26&gt;1,F26&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -1998,7 +2064,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F23 F20">
+  <conditionalFormatting sqref="F20 F23 F25">
     <cfRule type="containsText" dxfId="27" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -2030,7 +2096,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F21">
+  <conditionalFormatting sqref="F21 F24 F26">
     <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -2053,7 +2119,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -2586,6 +2652,48 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="7"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0100-000000000000}"/>
   <mergeCells count="2">
@@ -2593,7 +2701,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F23 F20">
+  <conditionalFormatting sqref="F20 F23 F25">
     <cfRule type="containsText" dxfId="24" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -2625,7 +2733,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F21">
+  <conditionalFormatting sqref="F21 F24 F26">
     <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -2648,7 +2756,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -3181,6 +3289,48 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7"/>
+      <c r="E25" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="14"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="2">
@@ -3188,7 +3338,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F23 F20">
+  <conditionalFormatting sqref="F20 F23 F25">
     <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -3220,7 +3370,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F21">
+  <conditionalFormatting sqref="F21 F24 F26">
     <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -3243,7 +3393,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -3820,6 +3970,52 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <mergeCells count="2">
@@ -3827,7 +4023,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F23 F20">
+  <conditionalFormatting sqref="F20 F23 F25">
     <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -3859,7 +4055,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F21">
+  <conditionalFormatting sqref="F21 F24 F26">
     <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -3882,7 +4078,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -4459,6 +4655,52 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" ref="G25:G26" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="8"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0400-000000000000}"/>
   <mergeCells count="2">
@@ -4466,7 +4708,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F23 F20">
+  <conditionalFormatting sqref="F20 F23 F25">
     <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -4498,7 +4740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F21">
+  <conditionalFormatting sqref="F21 F24 F26">
     <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -4518,7 +4760,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22 F19">
+  <conditionalFormatting sqref="F19 F22">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5122,7 +5364,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F23 F20">
+  <conditionalFormatting sqref="F20 F23">
     <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -5154,7 +5396,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24 F21">
+  <conditionalFormatting sqref="F21 F24">
     <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -5177,7 +5419,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -5755,6 +5997,52 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0600-000000000000}"/>
   <mergeCells count="2">
@@ -5762,7 +6050,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F23:F24 F20">
+  <conditionalFormatting sqref="F23:F26 F20">
     <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -5817,7 +6105,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="5" customWidth="1"/>
@@ -6395,6 +6683,52 @@
         <v/>
       </c>
     </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="12">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="F25" s="3">
+        <v>0</v>
+      </c>
+      <c r="G25" s="4" t="str">
+        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="12">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="E26" s="15"/>
+      <c r="F26" s="3">
+        <v>0</v>
+      </c>
+      <c r="G26" s="4" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="B2:E2" xr:uid="{00000000-0001-0000-0700-000000000000}"/>
   <mergeCells count="2">
@@ -6402,7 +6736,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F22 F20 F24">
+  <conditionalFormatting sqref="F20 F22 F24 F26">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -6434,7 +6768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23 F21">
+  <conditionalFormatting sqref="F21 F23 F25">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>

--- a/Collections/EURO/Austria/#EURO#Austria#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Austria/#EURO#Austria#Regular#[2002-present]#circulation_quality.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Austria\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8892D670-F24B-4414-98A2-B6F1BB278B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9B69FE0-04C2-427A-B52E-514DDF8DB278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1cent" sheetId="4" r:id="rId1"/>
@@ -1700,7 +1700,7 @@
         <v>158991000</v>
       </c>
       <c r="F10" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1722,7 +1722,7 @@
         <v>168565000</v>
       </c>
       <c r="F11" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11" s="4" t="str">
         <f t="shared" si="0"/>
@@ -1810,7 +1810,7 @@
         <v>185560000</v>
       </c>
       <c r="F15" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G15" s="4" t="str">
         <f t="shared" si="0"/>
@@ -2064,7 +2064,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F23 F25">
+  <conditionalFormatting sqref="F23 F20 F25">
     <cfRule type="containsText" dxfId="27" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -2096,7 +2096,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F24 F26">
+  <conditionalFormatting sqref="F24 F21 F26">
     <cfRule type="containsText" dxfId="25" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -2701,7 +2701,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F23 F25">
+  <conditionalFormatting sqref="F23 F20 F25">
     <cfRule type="containsText" dxfId="24" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -2733,7 +2733,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F24 F26">
+  <conditionalFormatting sqref="F24 F21 F26">
     <cfRule type="containsText" dxfId="22" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -3338,7 +3338,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F23 F25">
+  <conditionalFormatting sqref="F23 F20 F25">
     <cfRule type="containsText" dxfId="21" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -3370,7 +3370,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F24 F26">
+  <conditionalFormatting sqref="F24 F21 F26">
     <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -4023,7 +4023,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F23 F25">
+  <conditionalFormatting sqref="F23 F20 F25">
     <cfRule type="containsText" dxfId="18" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -4055,7 +4055,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F24 F26">
+  <conditionalFormatting sqref="F24 F21 F26">
     <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -4708,7 +4708,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F23 F25">
+  <conditionalFormatting sqref="F23 F20 F25">
     <cfRule type="containsText" dxfId="15" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -4740,7 +4740,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F24 F26">
+  <conditionalFormatting sqref="F24 F21 F26">
     <cfRule type="containsText" dxfId="13" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -4760,7 +4760,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19 F22">
+  <conditionalFormatting sqref="F22 F19">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5364,7 +5364,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F23">
+  <conditionalFormatting sqref="F23 F20">
     <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -5396,7 +5396,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F24">
+  <conditionalFormatting sqref="F24 F21">
     <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
@@ -6736,7 +6736,7 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <phoneticPr fontId="9" type="noConversion"/>
-  <conditionalFormatting sqref="F20 F22 F24 F26">
+  <conditionalFormatting sqref="F22 F20 F24 F26">
     <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
@@ -6768,7 +6768,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21 F23 F25">
+  <conditionalFormatting sqref="F23 F21 F25">
     <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
